--- a/artfynd/A 35487-2025 artfynd.xlsx
+++ b/artfynd/A 35487-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127723470</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127723473</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127723468</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127722925</v>
+        <v>127723472</v>
       </c>
       <c r="B5" t="n">
-        <v>97325</v>
+        <v>79020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445357</v>
+        <v>445301</v>
       </c>
       <c r="R5" t="n">
-        <v>6768567</v>
+        <v>6768568</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127723472</v>
+        <v>127722925</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>97327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445301</v>
+        <v>445357</v>
       </c>
       <c r="R6" t="n">
-        <v>6768568</v>
+        <v>6768567</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127723461</v>
+        <v>127723599</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>78687</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445368</v>
+        <v>445288</v>
       </c>
       <c r="R7" t="n">
-        <v>6768548</v>
+        <v>6768558</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127723599</v>
+        <v>127723461</v>
       </c>
       <c r="B8" t="n">
-        <v>78685</v>
+        <v>79020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445288</v>
+        <v>445368</v>
       </c>
       <c r="R8" t="n">
-        <v>6768558</v>
+        <v>6768548</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127723469</v>
+        <v>127723466</v>
       </c>
       <c r="B9" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445316</v>
+        <v>445349</v>
       </c>
       <c r="R9" t="n">
-        <v>6768572</v>
+        <v>6768591</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127723466</v>
+        <v>127723598</v>
       </c>
       <c r="B10" t="n">
-        <v>79018</v>
+        <v>78687</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445349</v>
+        <v>445303</v>
       </c>
       <c r="R10" t="n">
-        <v>6768591</v>
+        <v>6768564</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127723598</v>
+        <v>127723469</v>
       </c>
       <c r="B11" t="n">
-        <v>78685</v>
+        <v>79020</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445303</v>
+        <v>445316</v>
       </c>
       <c r="R11" t="n">
-        <v>6768564</v>
+        <v>6768572</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1648,7 +1648,7 @@
         <v>127722827</v>
       </c>
       <c r="B12" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127723596</v>
       </c>
       <c r="B13" t="n">
-        <v>78685</v>
+        <v>78687</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>127723471</v>
       </c>
       <c r="B14" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>127722867</v>
       </c>
       <c r="B15" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>127723464</v>
       </c>
       <c r="B16" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 35487-2025 artfynd.xlsx
+++ b/artfynd/A 35487-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127723470</v>
+        <v>127723473</v>
       </c>
       <c r="B2" t="n">
         <v>79020</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445293</v>
+        <v>445297</v>
       </c>
       <c r="R2" t="n">
-        <v>6768541</v>
+        <v>6768565</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127723473</v>
+        <v>127723470</v>
       </c>
       <c r="B3" t="n">
         <v>79020</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445297</v>
+        <v>445293</v>
       </c>
       <c r="R3" t="n">
-        <v>6768565</v>
+        <v>6768541</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127723598</v>
+        <v>127723469</v>
       </c>
       <c r="B10" t="n">
-        <v>78687</v>
+        <v>79020</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445303</v>
+        <v>445316</v>
       </c>
       <c r="R10" t="n">
-        <v>6768564</v>
+        <v>6768572</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127723469</v>
+        <v>127723598</v>
       </c>
       <c r="B11" t="n">
-        <v>79020</v>
+        <v>78687</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445316</v>
+        <v>445303</v>
       </c>
       <c r="R11" t="n">
-        <v>6768572</v>
+        <v>6768564</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 35487-2025 artfynd.xlsx
+++ b/artfynd/A 35487-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127723473</v>
+        <v>127723470</v>
       </c>
       <c r="B2" t="n">
         <v>79020</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445297</v>
+        <v>445293</v>
       </c>
       <c r="R2" t="n">
-        <v>6768565</v>
+        <v>6768541</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127723470</v>
+        <v>127723473</v>
       </c>
       <c r="B3" t="n">
         <v>79020</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445293</v>
+        <v>445297</v>
       </c>
       <c r="R3" t="n">
-        <v>6768541</v>
+        <v>6768565</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127723472</v>
+        <v>127722925</v>
       </c>
       <c r="B5" t="n">
-        <v>79020</v>
+        <v>97327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445301</v>
+        <v>445357</v>
       </c>
       <c r="R5" t="n">
-        <v>6768568</v>
+        <v>6768567</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127722925</v>
+        <v>127723472</v>
       </c>
       <c r="B6" t="n">
-        <v>97327</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445357</v>
+        <v>445301</v>
       </c>
       <c r="R6" t="n">
-        <v>6768567</v>
+        <v>6768568</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 35487-2025 artfynd.xlsx
+++ b/artfynd/A 35487-2025 artfynd.xlsx
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127722925</v>
+        <v>127723472</v>
       </c>
       <c r="B5" t="n">
-        <v>97327</v>
+        <v>79020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445357</v>
+        <v>445301</v>
       </c>
       <c r="R5" t="n">
-        <v>6768567</v>
+        <v>6768568</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127723472</v>
+        <v>127722925</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>97327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445301</v>
+        <v>445357</v>
       </c>
       <c r="R6" t="n">
-        <v>6768568</v>
+        <v>6768567</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127723469</v>
+        <v>127723598</v>
       </c>
       <c r="B10" t="n">
-        <v>79020</v>
+        <v>78687</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445316</v>
+        <v>445303</v>
       </c>
       <c r="R10" t="n">
-        <v>6768572</v>
+        <v>6768564</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127723598</v>
+        <v>127723469</v>
       </c>
       <c r="B11" t="n">
-        <v>78687</v>
+        <v>79020</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445303</v>
+        <v>445316</v>
       </c>
       <c r="R11" t="n">
-        <v>6768564</v>
+        <v>6768572</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 35487-2025 artfynd.xlsx
+++ b/artfynd/A 35487-2025 artfynd.xlsx
@@ -1066,7 +1066,7 @@
         <v>127722925</v>
       </c>
       <c r="B6" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127723466</v>
+        <v>127723598</v>
       </c>
       <c r="B9" t="n">
-        <v>79020</v>
+        <v>78687</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445349</v>
+        <v>445303</v>
       </c>
       <c r="R9" t="n">
-        <v>6768591</v>
+        <v>6768564</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127723598</v>
+        <v>127723469</v>
       </c>
       <c r="B10" t="n">
-        <v>78687</v>
+        <v>79020</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445303</v>
+        <v>445316</v>
       </c>
       <c r="R10" t="n">
-        <v>6768564</v>
+        <v>6768572</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,7 +1548,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127723469</v>
+        <v>127723466</v>
       </c>
       <c r="B11" t="n">
         <v>79020</v>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445316</v>
+        <v>445349</v>
       </c>
       <c r="R11" t="n">
-        <v>6768572</v>
+        <v>6768591</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 35487-2025 artfynd.xlsx
+++ b/artfynd/A 35487-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127723470</v>
       </c>
       <c r="B2" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127723473</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127723468</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127723472</v>
+        <v>127722925</v>
       </c>
       <c r="B5" t="n">
-        <v>79020</v>
+        <v>97336</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445301</v>
+        <v>445357</v>
       </c>
       <c r="R5" t="n">
-        <v>6768568</v>
+        <v>6768567</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127722925</v>
+        <v>127723472</v>
       </c>
       <c r="B6" t="n">
-        <v>97333</v>
+        <v>79023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445357</v>
+        <v>445301</v>
       </c>
       <c r="R6" t="n">
-        <v>6768567</v>
+        <v>6768568</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>127723599</v>
       </c>
       <c r="B7" t="n">
-        <v>78687</v>
+        <v>78690</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127723461</v>
       </c>
       <c r="B8" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>127723598</v>
       </c>
       <c r="B9" t="n">
-        <v>78687</v>
+        <v>78690</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127723469</v>
       </c>
       <c r="B10" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>127723466</v>
       </c>
       <c r="B11" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>127722827</v>
       </c>
       <c r="B12" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127723596</v>
       </c>
       <c r="B13" t="n">
-        <v>78687</v>
+        <v>78690</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>127723471</v>
       </c>
       <c r="B14" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>127722867</v>
       </c>
       <c r="B15" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>127723464</v>
       </c>
       <c r="B16" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 35487-2025 artfynd.xlsx
+++ b/artfynd/A 35487-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127723470</v>
       </c>
       <c r="B2" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127723473</v>
       </c>
       <c r="B3" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127723468</v>
       </c>
       <c r="B4" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127722925</v>
+        <v>127723472</v>
       </c>
       <c r="B5" t="n">
-        <v>97336</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445357</v>
+        <v>445301</v>
       </c>
       <c r="R5" t="n">
-        <v>6768567</v>
+        <v>6768568</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127723472</v>
+        <v>127722925</v>
       </c>
       <c r="B6" t="n">
-        <v>79023</v>
+        <v>97344</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445301</v>
+        <v>445357</v>
       </c>
       <c r="R6" t="n">
-        <v>6768568</v>
+        <v>6768567</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>127723599</v>
       </c>
       <c r="B7" t="n">
-        <v>78690</v>
+        <v>78696</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127723461</v>
       </c>
       <c r="B8" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>127723598</v>
       </c>
       <c r="B9" t="n">
-        <v>78690</v>
+        <v>78696</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127723469</v>
+        <v>127723466</v>
       </c>
       <c r="B10" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445316</v>
+        <v>445349</v>
       </c>
       <c r="R10" t="n">
-        <v>6768572</v>
+        <v>6768591</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127723466</v>
+        <v>127723469</v>
       </c>
       <c r="B11" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445349</v>
+        <v>445316</v>
       </c>
       <c r="R11" t="n">
-        <v>6768591</v>
+        <v>6768572</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1648,7 +1648,7 @@
         <v>127722827</v>
       </c>
       <c r="B12" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127723596</v>
       </c>
       <c r="B13" t="n">
-        <v>78690</v>
+        <v>78696</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>127723471</v>
       </c>
       <c r="B14" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>127722867</v>
       </c>
       <c r="B15" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>127723464</v>
       </c>
       <c r="B16" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 35487-2025 artfynd.xlsx
+++ b/artfynd/A 35487-2025 artfynd.xlsx
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127723472</v>
+        <v>127722925</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>97345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445301</v>
+        <v>445357</v>
       </c>
       <c r="R5" t="n">
-        <v>6768568</v>
+        <v>6768567</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127722925</v>
+        <v>127723472</v>
       </c>
       <c r="B6" t="n">
-        <v>97344</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445357</v>
+        <v>445301</v>
       </c>
       <c r="R6" t="n">
-        <v>6768567</v>
+        <v>6768568</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127723599</v>
+        <v>127723461</v>
       </c>
       <c r="B7" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445288</v>
+        <v>445368</v>
       </c>
       <c r="R7" t="n">
-        <v>6768558</v>
+        <v>6768548</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127723461</v>
+        <v>127723599</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445368</v>
+        <v>445288</v>
       </c>
       <c r="R8" t="n">
-        <v>6768548</v>
+        <v>6768558</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 35487-2025 artfynd.xlsx
+++ b/artfynd/A 35487-2025 artfynd.xlsx
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127722925</v>
+        <v>127723472</v>
       </c>
       <c r="B5" t="n">
-        <v>97345</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445357</v>
+        <v>445301</v>
       </c>
       <c r="R5" t="n">
-        <v>6768567</v>
+        <v>6768568</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127723472</v>
+        <v>127722925</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>97345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445301</v>
+        <v>445357</v>
       </c>
       <c r="R6" t="n">
-        <v>6768568</v>
+        <v>6768567</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127723461</v>
+        <v>127723599</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445368</v>
+        <v>445288</v>
       </c>
       <c r="R7" t="n">
-        <v>6768548</v>
+        <v>6768558</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127723599</v>
+        <v>127723461</v>
       </c>
       <c r="B8" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445288</v>
+        <v>445368</v>
       </c>
       <c r="R8" t="n">
-        <v>6768558</v>
+        <v>6768548</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,7 +1451,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127723466</v>
+        <v>127723469</v>
       </c>
       <c r="B10" t="n">
         <v>79029</v>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445349</v>
+        <v>445316</v>
       </c>
       <c r="R10" t="n">
-        <v>6768591</v>
+        <v>6768572</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,7 +1548,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127723469</v>
+        <v>127723466</v>
       </c>
       <c r="B11" t="n">
         <v>79029</v>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445316</v>
+        <v>445349</v>
       </c>
       <c r="R11" t="n">
-        <v>6768572</v>
+        <v>6768591</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 35487-2025 artfynd.xlsx
+++ b/artfynd/A 35487-2025 artfynd.xlsx
@@ -1066,7 +1066,7 @@
         <v>127722925</v>
       </c>
       <c r="B6" t="n">
-        <v>97345</v>
+        <v>97346</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127723599</v>
+        <v>127723461</v>
       </c>
       <c r="B7" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445288</v>
+        <v>445368</v>
       </c>
       <c r="R7" t="n">
-        <v>6768558</v>
+        <v>6768548</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127723461</v>
+        <v>127723599</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445368</v>
+        <v>445288</v>
       </c>
       <c r="R8" t="n">
-        <v>6768548</v>
+        <v>6768558</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,7 +1451,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127723469</v>
+        <v>127723466</v>
       </c>
       <c r="B10" t="n">
         <v>79029</v>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445316</v>
+        <v>445349</v>
       </c>
       <c r="R10" t="n">
-        <v>6768572</v>
+        <v>6768591</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,7 +1548,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127723466</v>
+        <v>127723469</v>
       </c>
       <c r="B11" t="n">
         <v>79029</v>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445349</v>
+        <v>445316</v>
       </c>
       <c r="R11" t="n">
-        <v>6768591</v>
+        <v>6768572</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 35487-2025 artfynd.xlsx
+++ b/artfynd/A 35487-2025 artfynd.xlsx
@@ -1066,7 +1066,7 @@
         <v>127722925</v>
       </c>
       <c r="B6" t="n">
-        <v>97346</v>
+        <v>97347</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127723461</v>
+        <v>127723599</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445368</v>
+        <v>445288</v>
       </c>
       <c r="R7" t="n">
-        <v>6768548</v>
+        <v>6768558</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127723599</v>
+        <v>127723461</v>
       </c>
       <c r="B8" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445288</v>
+        <v>445368</v>
       </c>
       <c r="R8" t="n">
-        <v>6768558</v>
+        <v>6768548</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,7 +1451,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127723466</v>
+        <v>127723469</v>
       </c>
       <c r="B10" t="n">
         <v>79029</v>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445349</v>
+        <v>445316</v>
       </c>
       <c r="R10" t="n">
-        <v>6768591</v>
+        <v>6768572</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,7 +1548,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127723469</v>
+        <v>127723466</v>
       </c>
       <c r="B11" t="n">
         <v>79029</v>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445316</v>
+        <v>445349</v>
       </c>
       <c r="R11" t="n">
-        <v>6768572</v>
+        <v>6768591</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 35487-2025 artfynd.xlsx
+++ b/artfynd/A 35487-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127723470</v>
+        <v>127723473</v>
       </c>
       <c r="B2" t="n">
         <v>79029</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445293</v>
+        <v>445297</v>
       </c>
       <c r="R2" t="n">
-        <v>6768541</v>
+        <v>6768565</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127723473</v>
+        <v>127723470</v>
       </c>
       <c r="B3" t="n">
         <v>79029</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445297</v>
+        <v>445293</v>
       </c>
       <c r="R3" t="n">
-        <v>6768565</v>
+        <v>6768541</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127723472</v>
+        <v>127722925</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>97347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445301</v>
+        <v>445357</v>
       </c>
       <c r="R5" t="n">
-        <v>6768568</v>
+        <v>6768567</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127722925</v>
+        <v>127723472</v>
       </c>
       <c r="B6" t="n">
-        <v>97347</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445357</v>
+        <v>445301</v>
       </c>
       <c r="R6" t="n">
-        <v>6768567</v>
+        <v>6768568</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1451,7 +1451,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127723469</v>
+        <v>127723466</v>
       </c>
       <c r="B10" t="n">
         <v>79029</v>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445316</v>
+        <v>445349</v>
       </c>
       <c r="R10" t="n">
-        <v>6768572</v>
+        <v>6768591</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,7 +1548,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127723466</v>
+        <v>127723469</v>
       </c>
       <c r="B11" t="n">
         <v>79029</v>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445349</v>
+        <v>445316</v>
       </c>
       <c r="R11" t="n">
-        <v>6768591</v>
+        <v>6768572</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 35487-2025 artfynd.xlsx
+++ b/artfynd/A 35487-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127723473</v>
+        <v>127723470</v>
       </c>
       <c r="B2" t="n">
         <v>79029</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445297</v>
+        <v>445293</v>
       </c>
       <c r="R2" t="n">
-        <v>6768565</v>
+        <v>6768541</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127723470</v>
+        <v>127723473</v>
       </c>
       <c r="B3" t="n">
         <v>79029</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445293</v>
+        <v>445297</v>
       </c>
       <c r="R3" t="n">
-        <v>6768541</v>
+        <v>6768565</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 35487-2025 artfynd.xlsx
+++ b/artfynd/A 35487-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127723470</v>
+        <v>127723473</v>
       </c>
       <c r="B2" t="n">
         <v>79029</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445293</v>
+        <v>445297</v>
       </c>
       <c r="R2" t="n">
-        <v>6768541</v>
+        <v>6768565</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127723473</v>
+        <v>127723470</v>
       </c>
       <c r="B3" t="n">
         <v>79029</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445297</v>
+        <v>445293</v>
       </c>
       <c r="R3" t="n">
-        <v>6768565</v>
+        <v>6768541</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127722925</v>
+        <v>127723472</v>
       </c>
       <c r="B5" t="n">
-        <v>97347</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445357</v>
+        <v>445301</v>
       </c>
       <c r="R5" t="n">
-        <v>6768567</v>
+        <v>6768568</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127723472</v>
+        <v>127722925</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>97347</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445301</v>
+        <v>445357</v>
       </c>
       <c r="R6" t="n">
-        <v>6768568</v>
+        <v>6768567</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127723598</v>
+        <v>127723466</v>
       </c>
       <c r="B9" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445303</v>
+        <v>445349</v>
       </c>
       <c r="R9" t="n">
-        <v>6768564</v>
+        <v>6768591</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127723466</v>
+        <v>127723598</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445349</v>
+        <v>445303</v>
       </c>
       <c r="R10" t="n">
-        <v>6768591</v>
+        <v>6768564</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 35487-2025 artfynd.xlsx
+++ b/artfynd/A 35487-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127723470</v>
+        <v>127723473</v>
       </c>
       <c r="B2" t="n">
         <v>79029</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445293</v>
+        <v>445297</v>
       </c>
       <c r="R2" t="n">
-        <v>6768541</v>
+        <v>6768565</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127723473</v>
+        <v>127723470</v>
       </c>
       <c r="B3" t="n">
         <v>79029</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445297</v>
+        <v>445293</v>
       </c>
       <c r="R3" t="n">
-        <v>6768565</v>
+        <v>6768541</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 35487-2025 artfynd.xlsx
+++ b/artfynd/A 35487-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127723470</v>
+        <v>127723473</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445293</v>
+        <v>445297</v>
       </c>
       <c r="R2" t="n">
-        <v>6768541</v>
+        <v>6768565</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127723473</v>
+        <v>127723470</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445297</v>
+        <v>445293</v>
       </c>
       <c r="R3" t="n">
-        <v>6768565</v>
+        <v>6768541</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>127723468</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127723472</v>
+        <v>127722925</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>97355</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445301</v>
+        <v>445357</v>
       </c>
       <c r="R5" t="n">
-        <v>6768568</v>
+        <v>6768567</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127722925</v>
+        <v>127723472</v>
       </c>
       <c r="B6" t="n">
-        <v>97347</v>
+        <v>79032</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445357</v>
+        <v>445301</v>
       </c>
       <c r="R6" t="n">
-        <v>6768567</v>
+        <v>6768568</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>127723599</v>
       </c>
       <c r="B7" t="n">
-        <v>78696</v>
+        <v>78699</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127723461</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>127723466</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127723598</v>
       </c>
       <c r="B10" t="n">
-        <v>78696</v>
+        <v>78699</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>127723469</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>127722827</v>
       </c>
       <c r="B12" t="n">
-        <v>79647</v>
+        <v>79650</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127723596</v>
       </c>
       <c r="B13" t="n">
-        <v>78696</v>
+        <v>78699</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>127723471</v>
       </c>
       <c r="B14" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>127723464</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 35487-2025 artfynd.xlsx
+++ b/artfynd/A 35487-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127723473</v>
+        <v>127723470</v>
       </c>
       <c r="B2" t="n">
         <v>79032</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445297</v>
+        <v>445293</v>
       </c>
       <c r="R2" t="n">
-        <v>6768565</v>
+        <v>6768541</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127723470</v>
+        <v>127723473</v>
       </c>
       <c r="B3" t="n">
         <v>79032</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445293</v>
+        <v>445297</v>
       </c>
       <c r="R3" t="n">
-        <v>6768541</v>
+        <v>6768565</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127723466</v>
+        <v>127723598</v>
       </c>
       <c r="B9" t="n">
-        <v>79032</v>
+        <v>78699</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445349</v>
+        <v>445303</v>
       </c>
       <c r="R9" t="n">
-        <v>6768591</v>
+        <v>6768564</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127723598</v>
+        <v>127723466</v>
       </c>
       <c r="B10" t="n">
-        <v>78699</v>
+        <v>79032</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445303</v>
+        <v>445349</v>
       </c>
       <c r="R10" t="n">
-        <v>6768564</v>
+        <v>6768591</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 35487-2025 artfynd.xlsx
+++ b/artfynd/A 35487-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127723470</v>
       </c>
       <c r="B2" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127723473</v>
       </c>
       <c r="B3" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127723468</v>
       </c>
       <c r="B4" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127722925</v>
+        <v>127723472</v>
       </c>
       <c r="B5" t="n">
-        <v>97355</v>
+        <v>79043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445357</v>
+        <v>445301</v>
       </c>
       <c r="R5" t="n">
-        <v>6768567</v>
+        <v>6768568</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127723472</v>
+        <v>127722925</v>
       </c>
       <c r="B6" t="n">
-        <v>79032</v>
+        <v>97367</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445301</v>
+        <v>445357</v>
       </c>
       <c r="R6" t="n">
-        <v>6768568</v>
+        <v>6768567</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>127723599</v>
       </c>
       <c r="B7" t="n">
-        <v>78699</v>
+        <v>78710</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127723461</v>
       </c>
       <c r="B8" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127723598</v>
+        <v>127723469</v>
       </c>
       <c r="B9" t="n">
-        <v>78699</v>
+        <v>79043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445303</v>
+        <v>445316</v>
       </c>
       <c r="R9" t="n">
-        <v>6768564</v>
+        <v>6768572</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1454,7 +1454,7 @@
         <v>127723466</v>
       </c>
       <c r="B10" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127723469</v>
+        <v>127723598</v>
       </c>
       <c r="B11" t="n">
-        <v>79032</v>
+        <v>78710</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445316</v>
+        <v>445303</v>
       </c>
       <c r="R11" t="n">
-        <v>6768572</v>
+        <v>6768564</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1648,7 +1648,7 @@
         <v>127722827</v>
       </c>
       <c r="B12" t="n">
-        <v>79650</v>
+        <v>79661</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127723596</v>
       </c>
       <c r="B13" t="n">
-        <v>78699</v>
+        <v>78710</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>127723471</v>
       </c>
       <c r="B14" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>127722867</v>
       </c>
       <c r="B15" t="n">
-        <v>56864</v>
+        <v>56875</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>127723464</v>
       </c>
       <c r="B16" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 35487-2025 artfynd.xlsx
+++ b/artfynd/A 35487-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127723470</v>
+        <v>127723595</v>
       </c>
       <c r="B2" t="n">
-        <v>79043</v>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445293</v>
+        <v>445374</v>
       </c>
       <c r="R2" t="n">
-        <v>6768541</v>
+        <v>6768578</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127723473</v>
+        <v>127723596</v>
       </c>
       <c r="B3" t="n">
-        <v>79043</v>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445297</v>
+        <v>445307</v>
       </c>
       <c r="R3" t="n">
-        <v>6768565</v>
+        <v>6768553</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127723468</v>
+        <v>127723598</v>
       </c>
       <c r="B4" t="n">
-        <v>79043</v>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445325</v>
+        <v>445303</v>
       </c>
       <c r="R4" t="n">
-        <v>6768598</v>
+        <v>6768564</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127723472</v>
+        <v>127723599</v>
       </c>
       <c r="B5" t="n">
-        <v>79043</v>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445301</v>
+        <v>445288</v>
       </c>
       <c r="R5" t="n">
-        <v>6768568</v>
+        <v>6768558</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127722925</v>
+        <v>127723422</v>
       </c>
       <c r="B6" t="n">
-        <v>97367</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445357</v>
+        <v>445332</v>
       </c>
       <c r="R6" t="n">
-        <v>6768567</v>
+        <v>6768518</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127723599</v>
+        <v>127723423</v>
       </c>
       <c r="B7" t="n">
-        <v>78710</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445288</v>
+        <v>445325</v>
       </c>
       <c r="R7" t="n">
-        <v>6768558</v>
+        <v>6768515</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1257,14 +1257,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127723461</v>
+        <v>127723460</v>
       </c>
       <c r="B8" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445368</v>
+        <v>445373</v>
       </c>
       <c r="R8" t="n">
-        <v>6768548</v>
+        <v>6768545</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,14 +1354,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127723469</v>
+        <v>127723461</v>
       </c>
       <c r="B9" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445316</v>
+        <v>445368</v>
       </c>
       <c r="R9" t="n">
-        <v>6768572</v>
+        <v>6768548</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,14 +1451,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127723466</v>
+        <v>127723462</v>
       </c>
       <c r="B10" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445349</v>
+        <v>445371</v>
       </c>
       <c r="R10" t="n">
-        <v>6768591</v>
+        <v>6768556</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127723598</v>
+        <v>127723463</v>
       </c>
       <c r="B11" t="n">
-        <v>78710</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445303</v>
+        <v>445370</v>
       </c>
       <c r="R11" t="n">
-        <v>6768564</v>
+        <v>6768559</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127722827</v>
+        <v>127723464</v>
       </c>
       <c r="B12" t="n">
-        <v>79661</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445293</v>
+        <v>445369</v>
       </c>
       <c r="R12" t="n">
-        <v>6768541</v>
+        <v>6768581</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127723596</v>
+        <v>127723465</v>
       </c>
       <c r="B13" t="n">
-        <v>78710</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>445307</v>
+        <v>445370</v>
       </c>
       <c r="R13" t="n">
-        <v>6768553</v>
+        <v>6768569</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,14 +1839,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127723471</v>
+        <v>127723466</v>
       </c>
       <c r="B14" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>445298</v>
+        <v>445349</v>
       </c>
       <c r="R14" t="n">
-        <v>6768554</v>
+        <v>6768591</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,32 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127722867</v>
+        <v>127723467</v>
       </c>
       <c r="B15" t="n">
-        <v>56875</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>445313</v>
+        <v>445334</v>
       </c>
       <c r="R15" t="n">
-        <v>6768547</v>
+        <v>6768612</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,14 +2033,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127723464</v>
+        <v>127723468</v>
       </c>
       <c r="B16" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445369</v>
+        <v>445325</v>
       </c>
       <c r="R16" t="n">
-        <v>6768581</v>
+        <v>6768598</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2127,6 +2127,1073 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127723469</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>445316</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6768572</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127723470</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>445293</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6768541</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127723471</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>445298</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6768554</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127723472</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>445301</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6768568</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127723473</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>445297</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6768565</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127723474</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>445289</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6768532</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127723477</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>445297</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6768511</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127722826</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>445327</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6768608</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127722827</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>445293</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6768541</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127722867</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>445313</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6768547</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127722925</v>
+      </c>
+      <c r="B27" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>445357</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6768567</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35487-2025 artfynd.xlsx
+++ b/artfynd/A 35487-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723595</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723596</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723598</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723599</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723422</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723423</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723460</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723461</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723462</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723463</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723464</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723465</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723466</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723467</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723468</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723469</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723470</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723471</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723472</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723473</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723474</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723477</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722826</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722827</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722867</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3194,8 +3324,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722925</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>